--- a/Configs/GameConfig/Datas/Enemy.xlsx
+++ b/Configs/GameConfig/Datas/Enemy.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterConfig" sheetId="1" r:id="R1dae5e7d085a4e82"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MonsterConfig" sheetId="1" r:id="R9b4cf44da32b4c87"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossConfig" sheetId="2" r:id="R6ce7cd2c11ea46a1"/>
   </sheets>
 </workbook>
 </file>
@@ -46,7 +47,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
@@ -55,6 +56,9 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </ext>
       </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1067,12 +1071,827 @@
       </c>
       <c r="AT6" s="1" t="inlineStr">
         <is>
-          <t>不掉落</t>
+          <t xml:space="preserve">不掉落</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7"/>
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+      <c r="AG7"/>
+      <c r="AH7"/>
+      <c r="AI7"/>
+      <c r="AJ7"/>
+      <c r="AK7"/>
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
+      <c r="AT7"/>
+    </row>
+    <row r="8">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8"/>
+      <c r="AI8"/>
+      <c r="AJ8"/>
+      <c r="AK8"/>
+      <c r="AL8"/>
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+      <c r="AR8"/>
+      <c r="AS8"/>
+      <c r="AT8"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
+    <mergeCell ref="H1:W1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FFA33A2B"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="11.818181991577148" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.818181991577148" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="11.818181991577148" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.545454025268555" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="9" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="9" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="9" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="9" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="9" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="9" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="9" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="9" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="9" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="9" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="9" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="9" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="9" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="9" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="9" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="9" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="9" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="9" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="9" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="9" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="9" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="9" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="9" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="9" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="9" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="9" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="9" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="9" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="9" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="9" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="9" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="9" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="9" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="9" hidden="0" customWidth="1"/>
+    <col min="41" max="41" width="9" hidden="0" customWidth="1"/>
+    <col min="42" max="42" width="9" hidden="0" customWidth="1"/>
+    <col min="43" max="43" width="9" hidden="0" customWidth="1"/>
+    <col min="44" max="44" width="9" hidden="0" customWidth="1"/>
+    <col min="45" max="45" width="9" hidden="0" customWidth="1"/>
+    <col min="46" max="46" width="9" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14" customHeight="1">
+      <c r="A1" s="1" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B1" s="1" t="str">
+        <v>Id</v>
+      </c>
+      <c r="C1" s="1" t="str">
+        <v>LegacyId</v>
+      </c>
+      <c r="D1" s="1" t="str">
+        <v>NameCn</v>
+      </c>
+      <c r="E1" s="1" t="str">
+        <v>Desc</v>
+      </c>
+      <c r="F1" s="1" t="str">
+        <v>EntityId</v>
+      </c>
+      <c r="G1" s="1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="H1" s="1" t="str">
+        <v>BaseAttributes</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1" t="str">
+        <v>MoveSpeed</v>
+      </c>
+      <c r="Y1" s="1" t="str">
+        <v>SightRange</v>
+      </c>
+      <c r="Z1" s="1" t="str">
+        <v>AttackDesire</v>
+      </c>
+      <c r="AA1" s="1" t="str">
+        <v>BehitCalmTime</v>
+      </c>
+      <c r="AB1" s="1" t="str">
+        <v>AddExp</v>
+      </c>
+      <c r="AC1" s="1" t="str">
+        <v>Gravity</v>
+      </c>
+      <c r="AD1" s="1" t="str">
+        <v>PatrolInterval</v>
+      </c>
+      <c r="AE1" s="1" t="str">
+        <v>PatrolIdleChance</v>
+      </c>
+      <c r="AF1" s="1" t="str">
+        <v>PatrolRadius</v>
+      </c>
+      <c r="AG1" s="1" t="str">
+        <v>AttackInterval</v>
+      </c>
+      <c r="AH1" s="1" t="str">
+        <v>AttackFirstDelay</v>
+      </c>
+      <c r="AI1" s="1" t="str">
+        <v>SuperArmor</v>
+      </c>
+      <c r="AJ1" s="1" t="str">
+        <v>AttackRangeSlack</v>
+      </c>
+      <c r="AK1" s="1" t="str">
+        <v>LoseTargetTime</v>
+      </c>
+      <c r="AL1" s="1" t="str">
+        <v>PaceRange</v>
+      </c>
+      <c r="AM1" s="1" t="str">
+        <v>SoulPerOrb</v>
+      </c>
+      <c r="AN1" s="1" t="str">
+        <v>SoulCount</v>
+      </c>
+      <c r="AO1" s="1" t="str">
+        <v>ManaDropChance</v>
+      </c>
+      <c r="AP1" s="1" t="str">
+        <v>ManaCount</v>
+      </c>
+      <c r="AQ1" s="1" t="str">
+        <v>MusouDropChance</v>
+      </c>
+      <c r="AR1" s="1" t="str">
+        <v>MusouCount</v>
+      </c>
+      <c r="AS1" s="1" t="str">
+        <v>EquipmentDropChance</v>
+      </c>
+      <c r="AT1" s="1" t="str">
+        <v>EquipmentDropPoolId</v>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="1" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1" t="str">
+        <v>MaxHp</v>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v>MaxMp</v>
+      </c>
+      <c r="J2" s="1" t="str">
+        <v>Power</v>
+      </c>
+      <c r="K2" s="1" t="str">
+        <v>Def</v>
+      </c>
+      <c r="L2" s="1" t="str">
+        <v>Mdef</v>
+      </c>
+      <c r="M2" s="1" t="str">
+        <v>Crit</v>
+      </c>
+      <c r="N2" s="1" t="str">
+        <v>Miss</v>
+      </c>
+      <c r="O2" s="1" t="str">
+        <v>Lucky</v>
+      </c>
+      <c r="P2" s="1" t="str">
+        <v>Toughness</v>
+      </c>
+      <c r="Q2" s="1" t="str">
+        <v>Htarget</v>
+      </c>
+      <c r="R2" s="1" t="str">
+        <v>CritReduce</v>
+      </c>
+      <c r="S2" s="1" t="str">
+        <v>Ar</v>
+      </c>
+      <c r="T2" s="1" t="str">
+        <v>Sp</v>
+      </c>
+      <c r="U2" s="1" t="str">
+        <v>Vampirism</v>
+      </c>
+      <c r="V2" s="1" t="str">
+        <v>HpRegen</v>
+      </c>
+      <c r="W2" s="1" t="str">
+        <v>MpRegen</v>
+      </c>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="1" t="str">
+        <v>##</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v>怪物ID</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>旧怪物编号</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <v>中文名</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <v>描述</v>
+      </c>
+      <c r="F3" s="1" t="str">
+        <v>实体枚举</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <v>等级(参与等级压制)</v>
+      </c>
+      <c r="H3" s="1" t="str">
+        <v>生命(旧 SHp)</v>
+      </c>
+      <c r="I3" s="1" t="str">
+        <v>魔法上限</v>
+      </c>
+      <c r="J3" s="1" t="str">
+        <v>攻击(填 0：怪物伤害由招式 FlatPower 决定)</v>
+      </c>
+      <c r="K3" s="1" t="str">
+        <v>物防</v>
+      </c>
+      <c r="L3" s="1" t="str">
+        <v>魔防</v>
+      </c>
+      <c r="M3" s="1" t="str">
+        <v>暴击</v>
+      </c>
+      <c r="N3" s="1" t="str">
+        <v>闪避</v>
+      </c>
+      <c r="O3" s="1" t="str">
+        <v>幸运</v>
+      </c>
+      <c r="P3" s="1" t="str">
+        <v>韧性(减对方幸运)</v>
+      </c>
+      <c r="Q3" s="1" t="str">
+        <v>命中(破闪)</v>
+      </c>
+      <c r="R3" s="1" t="str">
+        <v>暴击抵抗</v>
+      </c>
+      <c r="S3" s="1" t="str">
+        <v>破甲(减对方物防)</v>
+      </c>
+      <c r="T3" s="1" t="str">
+        <v>破魔(减对方魔防)</v>
+      </c>
+      <c r="U3" s="1" t="str">
+        <v>吸血(百分点,伤害转生命)</v>
+      </c>
+      <c r="V3" s="1" t="str">
+        <v>每秒回血(旧 self_rhp)</v>
+      </c>
+      <c r="W3" s="1" t="str">
+        <v>每秒回蓝</v>
+      </c>
+      <c r="X3" s="1" t="str">
+        <v>移动速度 px/s(旧 speed=8,代码里×10)</v>
+      </c>
+      <c r="Y3" s="1" t="str">
+        <v>索敌距离(旧 mysee)</v>
+      </c>
+      <c r="Z3" s="1" t="str">
+        <v>攻击欲望 0-100(旧 attackDesire)</v>
+      </c>
+      <c r="AA3" s="1" t="str">
+        <v>受击后僵直秒数(旧 behit_calmtime)</v>
+      </c>
+      <c r="AB3" s="1" t="str">
+        <v>击杀给英雄的经验(旧 add_exp)</v>
+      </c>
+      <c r="AC3" s="1" t="str">
+        <v>重力 px/s²；造一BaseObject.graity=1.5，按24fps换算为864</v>
+      </c>
+      <c r="AD3" s="1" t="str">
+        <v>巡逻重新决策间隔秒(旧 change_state 计时器 3s)</v>
+      </c>
+      <c r="AE3" s="1" t="str">
+        <v>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</v>
+      </c>
+      <c r="AF3" s="1" t="str">
+        <v>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</v>
+      </c>
+      <c r="AG3" s="1" t="str">
+        <v>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</v>
+      </c>
+      <c r="AH3" s="1" t="str">
+        <v>进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</v>
+      </c>
+      <c r="AI3" s="1" t="str">
+        <v>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</v>
+      </c>
+      <c r="AJ3" s="1" t="str">
+        <v>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</v>
+      </c>
+      <c r="AK3" s="1" t="str">
+        <v>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</v>
+      </c>
+      <c r="AL3" s="1" t="str">
+        <v>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</v>
+      </c>
+      <c r="AM3" s="1" t="str">
+        <v>每颗灵魂值（官方 gxp）</v>
+      </c>
+      <c r="AN3" s="1" t="str">
+        <v>灵魂球数量闭区间（官方均匀2～4）</v>
+      </c>
+      <c r="AO3" s="1" t="str">
+        <v>蓝球掉落概率（官方12%）</v>
+      </c>
+      <c r="AP3" s="1" t="str">
+        <v>触发后蓝球数量闭区间（官方1～3均匀）</v>
+      </c>
+      <c r="AQ3" s="1" t="str">
+        <v>白色无双球掉落概率（官方12%）</v>
+      </c>
+      <c r="AR3" s="1" t="str">
+        <v>触发后无双球数量闭区间（官方1～3均匀）</v>
+      </c>
+      <c r="AS3" s="1" t="str">
+        <v>装备掉落概率</v>
+      </c>
+      <c r="AT3" s="1" t="str">
+        <v>装备池</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <v>猕猴王</v>
+      </c>
+      <c r="E4" s="3" t="str">
+        <v>造一 Monster4；选招、无敌和动作阶段由专属状态控制</v>
+      </c>
+      <c r="F4" s="1" t="str">
+        <v>MacaqueKing</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z4" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>864</v>
+      </c>
+      <c r="AD4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF4" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="AG4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="AI4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN4" s="1" t="str">
+        <v>2,4</v>
+      </c>
+      <c r="AO4" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AP4" s="1" t="str">
+        <v>1,3</v>
+      </c>
+      <c r="AQ4" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AR4" s="1" t="str">
+        <v>1,3</v>
+      </c>
+      <c r="AS4" s="1" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AT4" s="1" t="str">
+        <v>猕猴王装备</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <v>禺狨王</v>
+      </c>
+      <c r="E5" s="3" t="str">
+        <v>造一 Monster6；选招、无敌和动作阶段由专属状态控制</v>
+      </c>
+      <c r="F5" s="1" t="str">
+        <v>TamarinKing</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z5" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>864</v>
+      </c>
+      <c r="AD5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF5" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="AG5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" s="1" t="str">
+        <v>0,0</v>
+      </c>
+      <c r="AI5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM5" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN5" s="1" t="str">
+        <v>2,4</v>
+      </c>
+      <c r="AO5" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AP5" s="1" t="str">
+        <v>1,3</v>
+      </c>
+      <c r="AQ5" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AR5" s="1" t="str">
+        <v>1,3</v>
+      </c>
+      <c r="AS5" s="1" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AT5" s="1" t="str">
+        <v>禺狨王装备</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+      <c r="AI6"/>
+      <c r="AJ6"/>
+      <c r="AK6"/>
+      <c r="AL6"/>
+      <c r="AM6"/>
+      <c r="AN6"/>
+      <c r="AO6"/>
+      <c r="AP6"/>
+      <c r="AQ6"/>
+      <c r="AR6"/>
+      <c r="AS6"/>
+      <c r="AT6"/>
+    </row>
+  </sheetData>
+  <mergeCells>
     <mergeCell ref="H1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
